--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130796210</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130796210</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,125 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131912069</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kägleån, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>372680</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6247867</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,443 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131928783</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 3317-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>372608</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6247858</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131928829</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58062</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 3317-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>372838</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6247770</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131928800</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58062</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 3317-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>372724</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6247835</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131928846</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57918</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 3317-2026, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>372838</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6247770</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Drog iväg en försiktig strof</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,6 +1344,249 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132034832</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58344</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kägleån, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>372795</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6247787</v>
+      </c>
+      <c r="S8" t="n">
+        <v>96</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132034827</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58063</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kägleån, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>372795</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6247787</v>
+      </c>
+      <c r="S9" t="n">
+        <v>96</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131928783</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58062</v>
+        <v>58064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58062</v>
+        <v>58064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131928846</v>
       </c>
       <c r="B7" t="n">
-        <v>57918</v>
+        <v>57920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B8" t="n">
-        <v>58344</v>
+        <v>58064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,8 +1381,16 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1435,6 +1443,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B9" t="n">
-        <v>58063</v>
+        <v>58345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,16 +1509,8 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1558,11 +1563,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131928783</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>57906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131928846</v>
       </c>
       <c r="B7" t="n">
-        <v>57920</v>
+        <v>57925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>132034827</v>
       </c>
       <c r="B8" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>132034832</v>
       </c>
       <c r="B9" t="n">
-        <v>58345</v>
+        <v>58350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B8" t="n">
-        <v>58069</v>
+        <v>58350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,16 +1381,8 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1443,11 +1435,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B9" t="n">
-        <v>58350</v>
+        <v>58069</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1509,8 +1496,16 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1563,6 +1558,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131928783</v>
       </c>
       <c r="B4" t="n">
-        <v>57906</v>
+        <v>57908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131928846</v>
       </c>
       <c r="B7" t="n">
-        <v>57925</v>
+        <v>57927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>132034832</v>
       </c>
       <c r="B8" t="n">
-        <v>58350</v>
+        <v>58352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>132034827</v>
       </c>
       <c r="B9" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B8" t="n">
-        <v>58352</v>
+        <v>58071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,8 +1381,16 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1435,6 +1443,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B9" t="n">
-        <v>58071</v>
+        <v>58352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,16 +1509,8 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1558,11 +1563,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58071</v>
+        <v>58105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131928783</v>
       </c>
       <c r="B4" t="n">
-        <v>57908</v>
+        <v>57942</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58071</v>
+        <v>58105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58071</v>
+        <v>58105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131928846</v>
       </c>
       <c r="B7" t="n">
-        <v>57927</v>
+        <v>57961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B8" t="n">
-        <v>58071</v>
+        <v>58386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,16 +1381,8 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1443,11 +1435,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B9" t="n">
-        <v>58352</v>
+        <v>58105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1509,8 +1496,16 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1563,6 +1558,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>132034832</v>
       </c>
       <c r="B8" t="n">
-        <v>58386</v>
+        <v>58388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>132034827</v>
       </c>
       <c r="B9" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131928783</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>57943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131928846</v>
       </c>
       <c r="B7" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B8" t="n">
-        <v>58388</v>
+        <v>58108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,8 +1381,16 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1435,6 +1443,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B9" t="n">
-        <v>58107</v>
+        <v>58389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,16 +1509,8 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1558,11 +1563,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>131912069</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>131928783</v>
       </c>
       <c r="B4" t="n">
-        <v>57943</v>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131928829</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131928846</v>
       </c>
       <c r="B7" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B8" t="n">
-        <v>58108</v>
+        <v>58393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,16 +1381,8 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1443,11 +1435,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B9" t="n">
-        <v>58389</v>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1472,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1509,8 +1496,16 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1563,6 +1558,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132034832</v>
+        <v>132034827</v>
       </c>
       <c r="B8" t="n">
-        <v>58393</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102999</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1381,8 +1381,16 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1435,6 +1443,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>17:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132034827</v>
+        <v>132034832</v>
       </c>
       <c r="B9" t="n">
-        <v>58112</v>
+        <v>58393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>102999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,16 +1509,8 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kägleån, Sk</t>
@@ -1558,11 +1563,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130796210</v>
+        <v>131928846</v>
       </c>
       <c r="B2" t="n">
-        <v>58041</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,21 +710,25 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kägleån, Sk</t>
+          <t>A 3317-2026, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372744</v>
+        <v>372838</v>
       </c>
       <c r="R2" t="n">
-        <v>6247742</v>
+        <v>6247770</v>
       </c>
       <c r="S2" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Drog iväg en försiktig strof</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,72 +777,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131912069</v>
+        <v>131928783</v>
       </c>
       <c r="B3" t="n">
-        <v>58112</v>
+        <v>57969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kägleån, Sk</t>
+          <t>A 3317-2026, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372680</v>
+        <v>372608</v>
       </c>
       <c r="R3" t="n">
-        <v>6247867</v>
+        <v>6247858</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:56</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:56</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,68 +882,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131928783</v>
+        <v>130796210</v>
       </c>
       <c r="B4" t="n">
-        <v>57947</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 3317-2026, Sk</t>
+          <t>Kägleån, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372608</v>
+        <v>372744</v>
       </c>
       <c r="R4" t="n">
-        <v>6247858</v>
+        <v>6247742</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,12 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,22 +997,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131928829</v>
+        <v>131912069</v>
       </c>
       <c r="B5" t="n">
-        <v>58112</v>
+        <v>58134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,23 +1046,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 3317-2026, Sk</t>
+          <t>Kägleån, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372838</v>
+        <v>372680</v>
       </c>
       <c r="R5" t="n">
-        <v>6247770</v>
+        <v>6247867</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,12 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1116,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1126,7 +1131,7 @@
         <v>131928800</v>
       </c>
       <c r="B6" t="n">
-        <v>58112</v>
+        <v>58134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131928846</v>
+        <v>131928829</v>
       </c>
       <c r="B7" t="n">
-        <v>57966</v>
+        <v>58134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,16 +1248,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1262,14 +1267,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1317,11 +1322,6 @@
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Drog iväg en försiktig strof</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1343,249 +1343,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>132034827</v>
-      </c>
-      <c r="B8" t="n">
-        <v>58112</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Poecile palustris</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Kägleån, Sk</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>372795</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6247787</v>
-      </c>
-      <c r="S8" t="n">
-        <v>96</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ängelholm</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Hjärnarp</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Frekvent</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>132034832</v>
-      </c>
-      <c r="B9" t="n">
-        <v>58393</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>102999</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Björktrast</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Turdus pilaris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Kägleån, Sk</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>372795</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6247787</v>
-      </c>
-      <c r="S9" t="n">
-        <v>96</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ängelholm</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Hjärnarp</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3317-2026 artfynd.xlsx
+++ b/artfynd/A 3317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130796210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131912069</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928800</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,8 +1373,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131928829</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>